--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0140.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0140.xlsx
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Mùa này, chủ đề tập trung vào những ý tưởng kinh doanh của các tín使 dưới tiêu đề "Đánh giá Vòng Kinh Doanh qua Trải nghiệm Người dùng."</t>
+          <t>Mùa này, chủ đề tập trung vào những ý tưởng kinh doanh của các tín sứ dưới tiêu đề "Đánh giá Vòng Kinh Doanh qua Trải nghiệm Người dùng."</t>
         </is>
       </c>
     </row>
@@ -30224,7 +30224,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Dạo này cậu sao rồi? Cuộc sống ở Kim Châu vẫn ổn chứ? Cậu biết là tớ luôn ở đây nếu cậu cần gì mà.</t>
+          <t>Dạo này cậu sao rồi? Cuộc sống ở Jinzhou vẫn ổn chứ? Cậu biết là tớ luôn ở đây nếu cậu cần gì mà.</t>
         </is>
       </c>
     </row>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Ôi, Yangyang! Có gì mà ngại chứ? Muốn gặp {PlayerName} thì bảo thẳng với {Male=anh ấy;Female=cô ấy} đi!</t>
+          <t>Ôi, Yangyang! Có gì mà ngại chứ? Muốn gặp {PlayerName} thì bảo thẳng với {Male=him;Female=her} đi!</t>
         </is>
       </c>
     </row>
@@ -30419,7 +30419,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Muốn đi xem pháo hoa không? Hay là bắn trăng? Lễ hội sắp tới rồi, có một chỗ cực cool để dẫn cậu đi xem.</t>
+          <t>Muốn đi xem pháo hoa không? Hay là bắn trăng? Lễ hội sắp tới rồi, có một chỗ cực cool để dẫn mày đi xem.</t>
         </is>
       </c>
     </row>
@@ -30809,7 +30809,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Muốn thử không, {PlayerName}? Chỉ cần viết điều ước của ngươi ra, đơn giản thôi! Yangyang, Baizhi và ta đã sẵn sàng rồi.</t>
+          <t>Muốn thử không, {PlayerName}? Chỉ cần viết điều ước của mày ra, đơn giản thôi! Yangyang, Baizhi và tao đã sẵn sàng rồi.</t>
         </is>
       </c>
     </row>
@@ -31199,7 +31199,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Nhiều quá, ta không biết chọn cái nào luôn...</t>
+          <t>Nhiều quá, tao không biết chọn cái nào luôn...</t>
         </is>
       </c>
     </row>
